--- a/backtest_runs/20260410_193731/by_symbol/HUMNL/HUMNL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/HUMNL/HUMNL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-2411.639999999994</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>107321.05</v>
@@ -679,7 +679,7 @@
         <v>-10077.21</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>97243.84000000001</v>
@@ -771,7 +771,7 @@
         <v>-689.0400000000006</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>104823.28</v>
@@ -909,7 +909,7 @@
         <v>-3272.940000000007</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>104909.41</v>
@@ -1047,7 +1047,7 @@
         <v>-1033.560000000009</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>105684.58</v>
@@ -1093,7 +1093,7 @@
         <v>-1119.689999999991</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>104564.89</v>
@@ -1185,7 +1185,7 @@
         <v>-6287.490000000003</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>101033.56</v>
@@ -1231,7 +1231,7 @@
         <v>-516.7800000000043</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>100516.78</v>
@@ -1277,7 +1277,7 @@
         <v>-5253.929999999995</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>95262.85000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-1808.730000000007</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>97588.36</v>
@@ -1461,7 +1461,7 @@
         <v>-947.4299999999951</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>96640.93000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-1550.339999999998</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>95090.59000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-4134.240000000003</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>99913.87</v>
